--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/141.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/141.xlsx
@@ -426,13 +426,13 @@
         <v>-15.27361159428836</v>
       </c>
       <c r="E2">
-        <v>-22.51927007763488</v>
+        <v>-23.22419498403888</v>
       </c>
       <c r="F2">
-        <v>-3.523553886613374</v>
+        <v>-4.173135415272553</v>
       </c>
       <c r="G2">
-        <v>-14.46155985677838</v>
+        <v>-15.70081954231254</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.1601921580533</v>
       </c>
       <c r="E3">
-        <v>-21.98438031327088</v>
+        <v>-22.20569589497374</v>
       </c>
       <c r="F3">
-        <v>-3.660530194945647</v>
+        <v>-4.569548091848454</v>
       </c>
       <c r="G3">
-        <v>-14.59911302393509</v>
+        <v>-13.92614532671205</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.09050597190356</v>
       </c>
       <c r="E4">
-        <v>-23.33530109381708</v>
+        <v>-23.08594972953273</v>
       </c>
       <c r="F4">
-        <v>-3.600005705975298</v>
+        <v>-4.107839220378985</v>
       </c>
       <c r="G4">
-        <v>-13.7750089912077</v>
+        <v>-15.77764571736963</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.03634182000483</v>
       </c>
       <c r="E5">
-        <v>-22.97767391600933</v>
+        <v>-23.64244484338732</v>
       </c>
       <c r="F5">
-        <v>-3.602880924064778</v>
+        <v>-3.80028115604177</v>
       </c>
       <c r="G5">
-        <v>-14.24611782944646</v>
+        <v>-15.30246987393588</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.96218555013261</v>
       </c>
       <c r="E6">
-        <v>-23.63302561745136</v>
+        <v>-22.05896428017721</v>
       </c>
       <c r="F6">
-        <v>-3.576565274720878</v>
+        <v>-4.452425912725088</v>
       </c>
       <c r="G6">
-        <v>-14.29563200380457</v>
+        <v>-14.42746454826942</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.83975528394072</v>
       </c>
       <c r="E7">
-        <v>-23.86626014274242</v>
+        <v>-25.09011647110739</v>
       </c>
       <c r="F7">
-        <v>-3.306013666509738</v>
+        <v>-3.848754434848583</v>
       </c>
       <c r="G7">
-        <v>-13.33539833850234</v>
+        <v>-14.25929214541999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.61469829774901</v>
       </c>
       <c r="E8">
-        <v>-24.18443978346935</v>
+        <v>-23.51853220911543</v>
       </c>
       <c r="F8">
-        <v>-3.181513793379297</v>
+        <v>-3.511074283999711</v>
       </c>
       <c r="G8">
-        <v>-14.70003169415424</v>
+        <v>-12.94456195322706</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.27771095396554</v>
       </c>
       <c r="E9">
-        <v>-25.52672929255693</v>
+        <v>-25.37086827416093</v>
       </c>
       <c r="F9">
-        <v>-3.480998916812558</v>
+        <v>-3.752198260743113</v>
       </c>
       <c r="G9">
-        <v>-14.42320884197869</v>
+        <v>-14.1156426086527</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.80022655506162</v>
       </c>
       <c r="E10">
-        <v>-25.30416838050196</v>
+        <v>-25.9034938015211</v>
       </c>
       <c r="F10">
-        <v>-3.452135084650717</v>
+        <v>-3.768005229485115</v>
       </c>
       <c r="G10">
-        <v>-12.8726999412061</v>
+        <v>-13.21414629758099</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.19131729311944</v>
       </c>
       <c r="E11">
-        <v>-25.63616439542629</v>
+        <v>-27.18413266546825</v>
       </c>
       <c r="F11">
-        <v>-3.354485361610636</v>
+        <v>-4.545611168789545</v>
       </c>
       <c r="G11">
-        <v>-13.13132306927951</v>
+        <v>-14.20685310407793</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.48199040903065</v>
       </c>
       <c r="E12">
-        <v>-25.88566067087889</v>
+        <v>-26.88792518062654</v>
       </c>
       <c r="F12">
-        <v>-3.067368189523999</v>
+        <v>-3.767417674590487</v>
       </c>
       <c r="G12">
-        <v>-13.45777596490704</v>
+        <v>-13.56363562434355</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.70161251545208</v>
       </c>
       <c r="E13">
-        <v>-28.07694848692451</v>
+        <v>-28.520027969257</v>
       </c>
       <c r="F13">
-        <v>-2.930619934843549</v>
+        <v>-3.202472557464223</v>
       </c>
       <c r="G13">
-        <v>-11.63299664256968</v>
+        <v>-12.67995004827312</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.92945440811541</v>
       </c>
       <c r="E14">
-        <v>-27.21585009741797</v>
+        <v>-27.05396620859177</v>
       </c>
       <c r="F14">
-        <v>-3.060746715091546</v>
+        <v>-3.04654245673597</v>
       </c>
       <c r="G14">
-        <v>-11.80993537000711</v>
+        <v>-12.36970558360586</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.21243357102731</v>
       </c>
       <c r="E15">
-        <v>-27.04091061802766</v>
+        <v>-29.56900368839376</v>
       </c>
       <c r="F15">
-        <v>-2.626666385169875</v>
+        <v>-3.320791226406704</v>
       </c>
       <c r="G15">
-        <v>-11.6471094982036</v>
+        <v>-10.9599925293457</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.612743408672396</v>
       </c>
       <c r="E16">
-        <v>-28.80077071536252</v>
+        <v>-30.72485139411154</v>
       </c>
       <c r="F16">
-        <v>-2.736442544404476</v>
+        <v>-3.258392421485432</v>
       </c>
       <c r="G16">
-        <v>-10.38685764340492</v>
+        <v>-11.46571146592477</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.169320871196589</v>
       </c>
       <c r="E17">
-        <v>-27.88364604543309</v>
+        <v>-29.87393301417425</v>
       </c>
       <c r="F17">
-        <v>-2.424015376230244</v>
+        <v>-3.3150209939038</v>
       </c>
       <c r="G17">
-        <v>-11.12074931018717</v>
+        <v>-11.1358917454838</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.883907307532315</v>
       </c>
       <c r="E18">
-        <v>-29.79825315655807</v>
+        <v>-28.77922423603403</v>
       </c>
       <c r="F18">
-        <v>-2.436018283363359</v>
+        <v>-2.377895484413774</v>
       </c>
       <c r="G18">
-        <v>-10.10824213081986</v>
+        <v>-11.40367184251883</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.770712706845217</v>
       </c>
       <c r="E19">
-        <v>-30.07701016681122</v>
+        <v>-31.60008994370703</v>
       </c>
       <c r="F19">
-        <v>-2.00702798425391</v>
+        <v>-2.15055133284061</v>
       </c>
       <c r="G19">
-        <v>-10.62400526256507</v>
+        <v>-10.07775862749425</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.791697823472552</v>
       </c>
       <c r="E20">
-        <v>-31.26240390119205</v>
+        <v>-31.65221720800932</v>
       </c>
       <c r="F20">
-        <v>-1.757301316977841</v>
+        <v>-2.648530237185474</v>
       </c>
       <c r="G20">
-        <v>-10.6152488696137</v>
+        <v>-11.03513529199608</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.924470310474868</v>
       </c>
       <c r="E21">
-        <v>-30.6065721815052</v>
+        <v>-32.74302017731793</v>
       </c>
       <c r="F21">
-        <v>-1.797172697104944</v>
+        <v>-2.541692644276972</v>
       </c>
       <c r="G21">
-        <v>-11.02378343134192</v>
+        <v>-11.18166003756422</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.128962401451949</v>
       </c>
       <c r="E22">
-        <v>-31.99466946941737</v>
+        <v>-33.66100299307181</v>
       </c>
       <c r="F22">
-        <v>-1.46494524572293</v>
+        <v>-2.26010894065888</v>
       </c>
       <c r="G22">
-        <v>-10.47913247922103</v>
+        <v>-10.65510452736098</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.35730908486755</v>
       </c>
       <c r="E23">
-        <v>-31.9981699798253</v>
+        <v>-31.57790947801746</v>
       </c>
       <c r="F23">
-        <v>-1.036780849248383</v>
+        <v>-1.548504737233346</v>
       </c>
       <c r="G23">
-        <v>-11.4095281975778</v>
+        <v>-11.38203080632861</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.589299718897607</v>
       </c>
       <c r="E24">
-        <v>-32.88006765044906</v>
+        <v>-33.24682423185627</v>
       </c>
       <c r="F24">
-        <v>-1.150664349774676</v>
+        <v>-1.533050934910488</v>
       </c>
       <c r="G24">
-        <v>-10.1610850587177</v>
+        <v>-10.26698278942791</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.781447557032315</v>
       </c>
       <c r="E25">
-        <v>-32.20302229427327</v>
+        <v>-32.81135485009368</v>
       </c>
       <c r="F25">
-        <v>-0.7973102614806997</v>
+        <v>-1.757029711413343</v>
       </c>
       <c r="G25">
-        <v>-10.81452715835013</v>
+        <v>-10.23456261696183</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.925708382077516</v>
       </c>
       <c r="E26">
-        <v>-33.27362147679666</v>
+        <v>-33.93094759290605</v>
       </c>
       <c r="F26">
-        <v>-1.074983003340613</v>
+        <v>-1.786345691614043</v>
       </c>
       <c r="G26">
-        <v>-10.76313093885294</v>
+        <v>-9.776604920877825</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.00670875046683</v>
       </c>
       <c r="E27">
-        <v>-32.22743982612263</v>
+        <v>-34.21521122755254</v>
       </c>
       <c r="F27">
-        <v>-0.8098437100954875</v>
+        <v>-1.788042632502436</v>
       </c>
       <c r="G27">
-        <v>-10.797024304084</v>
+        <v>-11.43537693714843</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.01594961253995</v>
       </c>
       <c r="E28">
-        <v>-33.54707337974984</v>
+        <v>-34.87280905210238</v>
       </c>
       <c r="F28">
-        <v>-0.9203943015227382</v>
+        <v>-1.98763708902527</v>
       </c>
       <c r="G28">
-        <v>-10.3282510557232</v>
+        <v>-11.18108731318593</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.965947718294132</v>
       </c>
       <c r="E29">
-        <v>-32.77817924951349</v>
+        <v>-34.64987001246777</v>
       </c>
       <c r="F29">
-        <v>-1.202392144237717</v>
+        <v>-1.764135008002962</v>
       </c>
       <c r="G29">
-        <v>-10.73570969015116</v>
+        <v>-10.32006076605904</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.850728803572231</v>
       </c>
       <c r="E30">
-        <v>-32.08166824781573</v>
+        <v>-32.91445914630032</v>
       </c>
       <c r="F30">
-        <v>-0.8958959547168053</v>
+        <v>-1.538811665177899</v>
       </c>
       <c r="G30">
-        <v>-10.27394817724254</v>
+        <v>-11.24296803040599</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.693452035164331</v>
       </c>
       <c r="E31">
-        <v>-31.49639694587939</v>
+        <v>-33.76581905245335</v>
       </c>
       <c r="F31">
-        <v>-0.7465667402441044</v>
+        <v>-1.29305772419071</v>
       </c>
       <c r="G31">
-        <v>-10.43483406936004</v>
+        <v>-10.9754693297418</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.503678153613764</v>
       </c>
       <c r="E32">
-        <v>-32.86325795493259</v>
+        <v>-33.0564992620249</v>
       </c>
       <c r="F32">
-        <v>-1.134445617494661</v>
+        <v>-1.456248324688295</v>
       </c>
       <c r="G32">
-        <v>-10.55772151977778</v>
+        <v>-9.573532746953392</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.295579022427974</v>
       </c>
       <c r="E33">
-        <v>-31.3352262917094</v>
+        <v>-33.16396900717493</v>
       </c>
       <c r="F33">
-        <v>-0.8851742656692803</v>
+        <v>-0.9741555743812034</v>
       </c>
       <c r="G33">
-        <v>-10.01286200328791</v>
+        <v>-10.56083674313024</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.092374651519409</v>
       </c>
       <c r="E34">
-        <v>-31.67400143222322</v>
+        <v>-31.55972086216565</v>
       </c>
       <c r="F34">
-        <v>-0.8713635582336905</v>
+        <v>-1.788626228132276</v>
       </c>
       <c r="G34">
-        <v>-10.23402299803893</v>
+        <v>-11.32370892556327</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.892901362078657</v>
       </c>
       <c r="E35">
-        <v>-30.65831905399085</v>
+        <v>-31.81355088724359</v>
       </c>
       <c r="F35">
-        <v>-0.9450264714785256</v>
+        <v>-1.639947124937863</v>
       </c>
       <c r="G35">
-        <v>-10.04414996917957</v>
+        <v>-11.82021461390655</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.719199837266379</v>
       </c>
       <c r="E36">
-        <v>-30.60696163026986</v>
+        <v>-32.63770145732154</v>
       </c>
       <c r="F36">
-        <v>-0.9110488529157299</v>
+        <v>-1.417122078194405</v>
       </c>
       <c r="G36">
-        <v>-10.56656729745872</v>
+        <v>-11.55448043401479</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.569880985649368</v>
       </c>
       <c r="E37">
-        <v>-30.31727514799919</v>
+        <v>-31.41887852781609</v>
       </c>
       <c r="F37">
-        <v>-1.252833177644463</v>
+        <v>-1.898891752494747</v>
       </c>
       <c r="G37">
-        <v>-10.75168969346922</v>
+        <v>-11.79592183073938</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.448095192125701</v>
       </c>
       <c r="E38">
-        <v>-30.41720045545244</v>
+        <v>-30.73380871569871</v>
       </c>
       <c r="F38">
-        <v>-1.423505996739542</v>
+        <v>-1.243637389246464</v>
       </c>
       <c r="G38">
-        <v>-11.49382461864426</v>
+        <v>-10.88465444450851</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.360787592458628</v>
       </c>
       <c r="E39">
-        <v>-30.26207078560868</v>
+        <v>-31.66499882589597</v>
       </c>
       <c r="F39">
-        <v>-1.163121780505523</v>
+        <v>-1.886447783264181</v>
       </c>
       <c r="G39">
-        <v>-10.50603728281868</v>
+        <v>-10.75637742595283</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.292545161500069</v>
       </c>
       <c r="E40">
-        <v>-29.97288922818986</v>
+        <v>-30.67321320500208</v>
       </c>
       <c r="F40">
-        <v>-1.063146385328619</v>
+        <v>-1.669590932263058</v>
       </c>
       <c r="G40">
-        <v>-10.59958005757633</v>
+        <v>-11.96158484007004</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.25420349687777</v>
       </c>
       <c r="E41">
-        <v>-29.23930813826532</v>
+        <v>-29.9170576721493</v>
       </c>
       <c r="F41">
-        <v>-1.343608033305622</v>
+        <v>-0.8894051360223767</v>
       </c>
       <c r="G41">
-        <v>-11.59273047717553</v>
+        <v>-10.65983860748214</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.232641445083662</v>
       </c>
       <c r="E42">
-        <v>-28.13341855780016</v>
+        <v>-29.41811493445818</v>
       </c>
       <c r="F42">
-        <v>-1.285725957655183</v>
+        <v>-1.477833444462777</v>
       </c>
       <c r="G42">
-        <v>-9.826170408691793</v>
+        <v>-11.5143632431699</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.227726437338648</v>
       </c>
       <c r="E43">
-        <v>-28.44848713688382</v>
+        <v>-28.26478958876267</v>
       </c>
       <c r="F43">
-        <v>-1.117899849943107</v>
+        <v>-1.584747847108178</v>
       </c>
       <c r="G43">
-        <v>-10.86433431598846</v>
+        <v>-9.844156602606654</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.241780363976227</v>
       </c>
       <c r="E44">
-        <v>-27.08386772246442</v>
+        <v>-28.56750449075341</v>
       </c>
       <c r="F44">
-        <v>-0.9430254590543679</v>
+        <v>-1.391070907738384</v>
       </c>
       <c r="G44">
-        <v>-10.7761347617312</v>
+        <v>-11.3658190648228</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.261827068934942</v>
       </c>
       <c r="E45">
-        <v>-25.90132013399742</v>
+        <v>-27.58600303433094</v>
       </c>
       <c r="F45">
-        <v>-1.011500151720223</v>
+        <v>-1.401238299715506</v>
       </c>
       <c r="G45">
-        <v>-10.96407774254116</v>
+        <v>-11.41089214233998</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.30247865825649</v>
       </c>
       <c r="E46">
-        <v>-27.03890903251627</v>
+        <v>-28.86798232658437</v>
       </c>
       <c r="F46">
-        <v>-0.9844995495678961</v>
+        <v>-1.714455737141542</v>
       </c>
       <c r="G46">
-        <v>-10.50569629662814</v>
+        <v>-10.44955275482764</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.353687300662836</v>
       </c>
       <c r="E47">
-        <v>-26.21749366073895</v>
+        <v>-27.57420183106695</v>
       </c>
       <c r="F47">
-        <v>-1.195787298717377</v>
+        <v>-1.338880671148035</v>
       </c>
       <c r="G47">
-        <v>-10.2872731230381</v>
+        <v>-9.630609862595966</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.424221904596381</v>
       </c>
       <c r="E48">
-        <v>-26.42069081793713</v>
+        <v>-28.0640740353207</v>
       </c>
       <c r="F48">
-        <v>-1.227101123930403</v>
+        <v>-0.8103251566937811</v>
       </c>
       <c r="G48">
-        <v>-10.53426961517759</v>
+        <v>-10.49548988473056</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.519276969545366</v>
       </c>
       <c r="E49">
-        <v>-25.38836629772657</v>
+        <v>-27.61847219296594</v>
       </c>
       <c r="F49">
-        <v>-1.348865936944881</v>
+        <v>-1.53292186287838</v>
       </c>
       <c r="G49">
-        <v>-10.87513000499203</v>
+        <v>-11.16640504371926</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.630667784675719</v>
       </c>
       <c r="E50">
-        <v>-25.79502779208938</v>
+        <v>-24.28335071274489</v>
       </c>
       <c r="F50">
-        <v>-1.310015255280278</v>
+        <v>-1.613623557064386</v>
       </c>
       <c r="G50">
-        <v>-10.24663286599801</v>
+        <v>-11.60388701564287</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.774376991195703</v>
       </c>
       <c r="E51">
-        <v>-25.26696696652894</v>
+        <v>-24.51222884604056</v>
       </c>
       <c r="F51">
-        <v>-0.755402235546341</v>
+        <v>-1.031991722560094</v>
       </c>
       <c r="G51">
-        <v>-10.57768079883405</v>
+        <v>-10.52397381855045</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.938151700358928</v>
       </c>
       <c r="E52">
-        <v>-24.7053682624677</v>
+        <v>-25.19589256697856</v>
       </c>
       <c r="F52">
-        <v>-1.495828302926957</v>
+        <v>-1.076039335186212</v>
       </c>
       <c r="G52">
-        <v>-10.1440059542806</v>
+        <v>-11.40593625566769</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.131698932927369</v>
       </c>
       <c r="E53">
-        <v>-24.29223557874794</v>
+        <v>-25.83092953402219</v>
       </c>
       <c r="F53">
-        <v>-1.124052547424589</v>
+        <v>-1.15119409940339</v>
       </c>
       <c r="G53">
-        <v>-11.11188366923301</v>
+        <v>-10.67526243914961</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.355748509703556</v>
       </c>
       <c r="E54">
-        <v>-24.24354995469147</v>
+        <v>-24.98004285340295</v>
       </c>
       <c r="F54">
-        <v>-1.013826615710004</v>
+        <v>-1.621960185003259</v>
       </c>
       <c r="G54">
-        <v>-11.40924018011588</v>
+        <v>-10.67283249872378</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.601672804004137</v>
       </c>
       <c r="E55">
-        <v>-23.78194901366761</v>
+        <v>-23.81784169865241</v>
       </c>
       <c r="F55">
-        <v>-1.367415884332423</v>
+        <v>-1.778810418868382</v>
       </c>
       <c r="G55">
-        <v>-10.40353948237731</v>
+        <v>-9.778981892575022</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.88309923550068</v>
       </c>
       <c r="E56">
-        <v>-22.58920783020934</v>
+        <v>-23.8111667279651</v>
       </c>
       <c r="F56">
-        <v>-1.402802209307002</v>
+        <v>-1.352372261841664</v>
       </c>
       <c r="G56">
-        <v>-10.80272175295709</v>
+        <v>-11.27980116007592</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.18159003426392</v>
       </c>
       <c r="E57">
-        <v>-23.21383383550933</v>
+        <v>-22.74267328585528</v>
       </c>
       <c r="F57">
-        <v>-0.6101494800999813</v>
+        <v>-1.772707608123236</v>
       </c>
       <c r="G57">
-        <v>-11.02438595063007</v>
+        <v>-11.4992572238742</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.50678438556176</v>
       </c>
       <c r="E58">
-        <v>-22.2751581577774</v>
+        <v>-22.45761943249445</v>
       </c>
       <c r="F58">
-        <v>-0.9768518337022389</v>
+        <v>-1.428738561084154</v>
       </c>
       <c r="G58">
-        <v>-11.35032902224455</v>
+        <v>-11.17787608401284</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.85226663752067</v>
       </c>
       <c r="E59">
-        <v>-23.54811220133354</v>
+        <v>-22.98411340604823</v>
       </c>
       <c r="F59">
-        <v>-1.173127634479269</v>
+        <v>-1.207011814393054</v>
       </c>
       <c r="G59">
-        <v>-11.93978489769394</v>
+        <v>-10.37896861338483</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.20754054591835</v>
       </c>
       <c r="E60">
-        <v>-22.58673981187516</v>
+        <v>-22.72906974993624</v>
       </c>
       <c r="F60">
-        <v>-0.9005488826963663</v>
+        <v>-1.583406448197801</v>
       </c>
       <c r="G60">
-        <v>-10.72856553287741</v>
+        <v>-11.50720253316846</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.58195715190066</v>
       </c>
       <c r="E61">
-        <v>-22.54304003770114</v>
+        <v>-21.5854715664092</v>
       </c>
       <c r="F61">
-        <v>-0.9824716141431759</v>
+        <v>-0.6236117722341743</v>
       </c>
       <c r="G61">
-        <v>-12.05832891236417</v>
+        <v>-10.70417012279852</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.95182907404763</v>
       </c>
       <c r="E62">
-        <v>-22.47256792519378</v>
+        <v>-23.46590228419829</v>
       </c>
       <c r="F62">
-        <v>-0.9745222023006276</v>
+        <v>-1.813696292773682</v>
       </c>
       <c r="G62">
-        <v>-12.04324606688725</v>
+        <v>-12.61835403796944</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.32599492884507</v>
       </c>
       <c r="E63">
-        <v>-22.14324823840797</v>
+        <v>-20.38101974916709</v>
       </c>
       <c r="F63">
-        <v>-1.657770151310218</v>
+        <v>-1.530224811704387</v>
       </c>
       <c r="G63">
-        <v>-12.25687225999088</v>
+        <v>-13.33132967803458</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.68983024992623</v>
       </c>
       <c r="E64">
-        <v>-21.38710629097721</v>
+        <v>-21.64882944625052</v>
       </c>
       <c r="F64">
-        <v>-1.04780740168463</v>
+        <v>-1.557350526624034</v>
       </c>
       <c r="G64">
-        <v>-12.00270843675887</v>
+        <v>-13.37598231626827</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.02952517807649</v>
       </c>
       <c r="E65">
-        <v>-20.88754768082106</v>
+        <v>-20.56473993965828</v>
       </c>
       <c r="F65">
-        <v>-1.015609868570789</v>
+        <v>-1.998702442256445</v>
       </c>
       <c r="G65">
-        <v>-11.53141255269715</v>
+        <v>-11.89110001499342</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.34560754202783</v>
       </c>
       <c r="E66">
-        <v>-21.08401552564384</v>
+        <v>-20.42711961456518</v>
       </c>
       <c r="F66">
-        <v>-1.478479596476276</v>
+        <v>-1.711745224467268</v>
       </c>
       <c r="G66">
-        <v>-12.25345246644881</v>
+        <v>-14.14722355782458</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.60872077008146</v>
       </c>
       <c r="E67">
-        <v>-21.87539805780228</v>
+        <v>-21.32166531309237</v>
       </c>
       <c r="F67">
-        <v>-1.121602554373405</v>
+        <v>-2.020143444792622</v>
       </c>
       <c r="G67">
-        <v>-11.97467142658678</v>
+        <v>-13.62323372041427</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.82393629206072</v>
       </c>
       <c r="E68">
-        <v>-20.90582460191601</v>
+        <v>-21.56682783891963</v>
       </c>
       <c r="F68">
-        <v>-1.028548745899929</v>
+        <v>-1.885043036117187</v>
       </c>
       <c r="G68">
-        <v>-12.64452390045738</v>
+        <v>-12.71226759382748</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.97272605167729</v>
       </c>
       <c r="E69">
-        <v>-21.10875457914774</v>
+        <v>-21.02622314035795</v>
       </c>
       <c r="F69">
-        <v>-1.548168199726316</v>
+        <v>-1.71804362289297</v>
       </c>
       <c r="G69">
-        <v>-12.20102335674337</v>
+        <v>-12.91267146804726</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.04759793583708</v>
       </c>
       <c r="E70">
-        <v>-21.58626857783456</v>
+        <v>-19.61805339140678</v>
       </c>
       <c r="F70">
-        <v>-1.307313452988538</v>
+        <v>-1.691267906980636</v>
       </c>
       <c r="G70">
-        <v>-12.22814996689216</v>
+        <v>-12.37373782807269</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.05544367667302</v>
       </c>
       <c r="E71">
-        <v>-21.49711198157154</v>
+        <v>-21.55875356976395</v>
       </c>
       <c r="F71">
-        <v>-1.891918695349067</v>
+        <v>-2.228853712564725</v>
       </c>
       <c r="G71">
-        <v>-12.02502813478464</v>
+        <v>-11.70611004080449</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.98144154033106</v>
       </c>
       <c r="E72">
-        <v>-20.67360445480268</v>
+        <v>-21.43544322253508</v>
       </c>
       <c r="F72">
-        <v>-1.346953612051987</v>
+        <v>-1.175304438260041</v>
       </c>
       <c r="G72">
-        <v>-12.32211980202437</v>
+        <v>-12.66083495832937</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.8505877977654</v>
       </c>
       <c r="E73">
-        <v>-21.93364329048894</v>
+        <v>-22.49546388977656</v>
       </c>
       <c r="F73">
-        <v>-1.804461703580755</v>
+        <v>-2.436801425938544</v>
       </c>
       <c r="G73">
-        <v>-12.23366533576059</v>
+        <v>-12.14348938581638</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.66283586178734</v>
       </c>
       <c r="E74">
-        <v>-21.690441593907</v>
+        <v>-20.81167762729655</v>
       </c>
       <c r="F74">
-        <v>-1.824098073226288</v>
+        <v>-1.887923005324413</v>
       </c>
       <c r="G74">
-        <v>-12.30521946704639</v>
+        <v>-13.13943059530518</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.43509345471789</v>
       </c>
       <c r="E75">
-        <v>-22.45441780137103</v>
+        <v>-22.73338085719154</v>
       </c>
       <c r="F75">
-        <v>-1.800363864524555</v>
+        <v>-2.381438234546612</v>
       </c>
       <c r="G75">
-        <v>-11.85143967943295</v>
+        <v>-12.2528532577062</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.19029492793476</v>
       </c>
       <c r="E76">
-        <v>-21.68184655024044</v>
+        <v>-21.59780260113209</v>
       </c>
       <c r="F76">
-        <v>-1.947807677104925</v>
+        <v>-2.264211530832826</v>
       </c>
       <c r="G76">
-        <v>-11.73477936517457</v>
+        <v>-12.52746301018875</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.92652572326278</v>
       </c>
       <c r="E77">
-        <v>-23.06180843459783</v>
+        <v>-22.44516612897336</v>
       </c>
       <c r="F77">
-        <v>-2.000578341913283</v>
+        <v>-2.166913390505973</v>
       </c>
       <c r="G77">
-        <v>-11.21724178102031</v>
+        <v>-11.76910310132574</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.67799130649581</v>
       </c>
       <c r="E78">
-        <v>-22.22097496627562</v>
+        <v>-21.6635198159314</v>
       </c>
       <c r="F78">
-        <v>-2.002184219711538</v>
+        <v>-2.484441675433836</v>
       </c>
       <c r="G78">
-        <v>-11.86506919541813</v>
+        <v>-12.51298599454551</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.4424176076792</v>
       </c>
       <c r="E79">
-        <v>-23.28215039438905</v>
+        <v>-22.52140298889249</v>
       </c>
       <c r="F79">
-        <v>-2.050617114017508</v>
+        <v>-2.437403234186411</v>
       </c>
       <c r="G79">
-        <v>-11.48069830558105</v>
+        <v>-10.05907721901614</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.23644936058929</v>
       </c>
       <c r="E80">
-        <v>-23.90310380726882</v>
+        <v>-23.68879830332983</v>
       </c>
       <c r="F80">
-        <v>-2.461115271005328</v>
+        <v>-2.470222371872063</v>
       </c>
       <c r="G80">
-        <v>-11.90353442403892</v>
+        <v>-11.03416861269861</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.07276307092139</v>
       </c>
       <c r="E81">
-        <v>-24.38583007953847</v>
+        <v>-23.75674805581493</v>
       </c>
       <c r="F81">
-        <v>-1.811330236136016</v>
+        <v>-2.401704127293533</v>
       </c>
       <c r="G81">
-        <v>-11.51927278220464</v>
+        <v>-10.38031600541932</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.94034385769027</v>
       </c>
       <c r="E82">
-        <v>-25.03970096998</v>
+        <v>-25.01291051775062</v>
       </c>
       <c r="F82">
-        <v>-2.101418440520017</v>
+        <v>-2.680035690814269</v>
       </c>
       <c r="G82">
-        <v>-10.59381308724692</v>
+        <v>-10.66195735662728</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.86387160503438</v>
       </c>
       <c r="E83">
-        <v>-25.68604553662078</v>
+        <v>-27.72816994732775</v>
       </c>
       <c r="F83">
-        <v>-2.522558309406632</v>
+        <v>-2.404478780057382</v>
       </c>
       <c r="G83">
-        <v>-10.99307812146518</v>
+        <v>-11.20140744170598</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.82718617615756</v>
       </c>
       <c r="E84">
-        <v>-26.73923273658468</v>
+        <v>-26.98363900725266</v>
       </c>
       <c r="F84">
-        <v>-2.647321077719036</v>
+        <v>-2.533131130098106</v>
       </c>
       <c r="G84">
-        <v>-11.36910974708884</v>
+        <v>-11.96740808967362</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.84152292885501</v>
       </c>
       <c r="E85">
-        <v>-27.40999936354883</v>
+        <v>-26.72255889528844</v>
       </c>
       <c r="F85">
-        <v>-2.070893300852879</v>
+        <v>-2.659919458276357</v>
       </c>
       <c r="G85">
-        <v>-11.18843341373757</v>
+        <v>-10.86789646298872</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.90806343400537</v>
       </c>
       <c r="E86">
-        <v>-28.17305176231529</v>
+        <v>-28.46851204894574</v>
       </c>
       <c r="F86">
-        <v>-2.359294858436937</v>
+        <v>-2.649728310710505</v>
       </c>
       <c r="G86">
-        <v>-10.34057621676591</v>
+        <v>-9.648933732155832</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.01356391144946</v>
       </c>
       <c r="E87">
-        <v>-29.38373928826596</v>
+        <v>-30.81153091509236</v>
       </c>
       <c r="F87">
-        <v>-2.30028043305696</v>
+        <v>-2.337673313426401</v>
       </c>
       <c r="G87">
-        <v>-9.796974707580961</v>
+        <v>-9.992336620944432</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.17834495499528</v>
       </c>
       <c r="E88">
-        <v>-30.22259381344682</v>
+        <v>-29.12046739488203</v>
       </c>
       <c r="F88">
-        <v>-2.606687935046607</v>
+        <v>-2.949390017353337</v>
       </c>
       <c r="G88">
-        <v>-10.15015694789257</v>
+        <v>-9.225597721321529</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.38292496673578</v>
       </c>
       <c r="E89">
-        <v>-31.50066503263162</v>
+        <v>-30.30315536604327</v>
       </c>
       <c r="F89">
-        <v>-2.792798719405389</v>
+        <v>-3.440052992221829</v>
       </c>
       <c r="G89">
-        <v>-9.36481278233896</v>
+        <v>-9.199040525005495</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.64212406821123</v>
       </c>
       <c r="E90">
-        <v>-31.83695404091523</v>
+        <v>-31.68574150108811</v>
       </c>
       <c r="F90">
-        <v>-2.714001431582699</v>
+        <v>-2.705021819042158</v>
       </c>
       <c r="G90">
-        <v>-10.07771890094778</v>
+        <v>-9.434155469204535</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.95115719116325</v>
       </c>
       <c r="E91">
-        <v>-32.94959557612583</v>
+        <v>-33.48819642493911</v>
       </c>
       <c r="F91">
-        <v>-2.686098908911529</v>
+        <v>-3.278400962021094</v>
       </c>
       <c r="G91">
-        <v>-9.89600636684272</v>
+        <v>-11.3393148372354</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.29429913325807</v>
       </c>
       <c r="E92">
-        <v>-35.05362649075465</v>
+        <v>-34.49359237446306</v>
       </c>
       <c r="F92">
-        <v>-2.883120635174731</v>
+        <v>-4.09947171017476</v>
       </c>
       <c r="G92">
-        <v>-9.875050613579132</v>
+        <v>-10.96456770328098</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.67675524958729</v>
       </c>
       <c r="E93">
-        <v>-36.45955238083501</v>
+        <v>-36.23520951425802</v>
       </c>
       <c r="F93">
-        <v>-3.219862440268705</v>
+        <v>-3.223888220705752</v>
       </c>
       <c r="G93">
-        <v>-9.691798675798315</v>
+        <v>-11.06971062960823</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.05881257698358</v>
       </c>
       <c r="E94">
-        <v>-37.93176154496565</v>
+        <v>-39.72569840920823</v>
       </c>
       <c r="F94">
-        <v>-3.273726654011675</v>
+        <v>-3.114195206031713</v>
       </c>
       <c r="G94">
-        <v>-9.91158248360499</v>
+        <v>-10.14905122568245</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.43650736554012</v>
       </c>
       <c r="E95">
-        <v>-39.50205519186542</v>
+        <v>-37.4263612033396</v>
       </c>
       <c r="F95">
-        <v>-3.220507800429247</v>
+        <v>-3.196352325954007</v>
       </c>
       <c r="G95">
-        <v>-9.727069227973711</v>
+        <v>-10.2971782752916</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.77525151982241</v>
       </c>
       <c r="E96">
-        <v>-40.85256840975093</v>
+        <v>-41.43696118772978</v>
       </c>
       <c r="F96">
-        <v>-3.222937205303531</v>
+        <v>-3.795286939437432</v>
       </c>
       <c r="G96">
-        <v>-10.29662872473208</v>
+        <v>-10.12693016038904</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.04859142257966</v>
       </c>
       <c r="E97">
-        <v>-42.79563924425112</v>
+        <v>-42.38508099800471</v>
       </c>
       <c r="F97">
-        <v>-3.344674303464489</v>
+        <v>-4.002034995580305</v>
       </c>
       <c r="G97">
-        <v>-10.58180904912152</v>
+        <v>-11.09369222149471</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.23979246895336</v>
       </c>
       <c r="E98">
-        <v>-45.72147497942192</v>
+        <v>-46.08021389759855</v>
       </c>
       <c r="F98">
-        <v>-3.765963040707155</v>
+        <v>-4.302893192042253</v>
       </c>
       <c r="G98">
-        <v>-10.32840665136355</v>
+        <v>-10.22619355783855</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.32295699335793</v>
       </c>
       <c r="E99">
-        <v>-46.20070753399465</v>
+        <v>-46.83013825021678</v>
       </c>
       <c r="F99">
-        <v>-4.077360008183394</v>
+        <v>-4.011398656805341</v>
       </c>
       <c r="G99">
-        <v>-10.42984507723236</v>
+        <v>-9.805459635798114</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-15.28543773613856</v>
       </c>
       <c r="E100">
-        <v>-47.815622499529</v>
+        <v>-49.94702577529718</v>
       </c>
       <c r="F100">
-        <v>-4.302182899939178</v>
+        <v>-4.267538541185982</v>
       </c>
       <c r="G100">
-        <v>-10.96211458903638</v>
+        <v>-11.41282550093491</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.14618603011158</v>
       </c>
       <c r="E101">
-        <v>-49.99885529243347</v>
+        <v>-51.14928128264557</v>
       </c>
       <c r="F101">
-        <v>-4.527701830444798</v>
+        <v>-4.004621979193176</v>
       </c>
       <c r="G101">
-        <v>-10.38562943100985</v>
+        <v>-12.33705698349756</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.8518381307583</v>
       </c>
       <c r="E102">
-        <v>-51.83634022697081</v>
+        <v>-54.16618236587362</v>
       </c>
       <c r="F102">
-        <v>-4.739145574626949</v>
+        <v>-4.410478294142843</v>
       </c>
       <c r="G102">
-        <v>-11.24681488432262</v>
+        <v>-11.15548024343967</v>
       </c>
     </row>
   </sheetData>
